--- a/doisoat/Ton-Huy 4-5 (Sao chép).xlsx
+++ b/doisoat/Ton-Huy 4-5 (Sao chép).xlsx
@@ -10146,9 +10146,6 @@
         <f aca="false">VLOOKUP(A7,CODE!D:E,2,0)</f>
         <v>Kg</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>15</v>
-      </c>
       <c r="F7" s="1" t="n">
         <v>0</v>
       </c>
@@ -10191,9 +10188,6 @@
       <c r="D9" s="1" t="str">
         <f aca="false">VLOOKUP(A9,CODE!D:E,2,0)</f>
         <v>Kg</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>0</v>
